--- a/Supply_Chain_Diagnostic_Ishita.xlsx
+++ b/Supply_Chain_Diagnostic_Ishita.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F0BA4EF-C1C1-492B-8C6F-4EEA32C5EDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C003AEB4-4BEC-40D5-BA17-15005D505743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{5F94F000-157C-4A98-8256-89DDA84D716F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{5F94F000-157C-4A98-8256-89DDA84D716F}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="3" r:id="rId1"/>
     <sheet name="Detail2" sheetId="6" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
     <sheet name="Recommendations" sheetId="7" r:id="rId4"/>
-    <sheet name="claude project" sheetId="1" r:id="rId5"/>
+    <sheet name="Project Data  " sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
@@ -1472,7 +1472,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Hp" refreshedDate="46165.619110648149" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{721C5409-BD72-47B4-AA8B-C3670A5AC698}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:Y101" sheet="claude project"/>
+    <worksheetSource ref="A1:Y101" sheet="Project Data  "/>
   </cacheSource>
   <cacheFields count="25">
     <cacheField name="Product type" numFmtId="0">
